--- a/sheets/대금율보/검수/긴아리랑.xlsx
+++ b/sheets/대금율보/검수/긴아리랑.xlsx
@@ -6698,8 +6698,7 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南∧
-–Z
-‹</t>
+–Z</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
@@ -6717,8 +6716,7 @@
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰И∼
-‹</t>
+汰И∼</t>
         </is>
       </c>
       <c r="K5" s="24"/>
@@ -6747,8 +6745,7 @@
       <c r="S5" s="24"/>
       <c r="T5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">)
-‹</t>
+          <t xml:space="preserve">)</t>
         </is>
       </c>
       <c r="U5" s="24"/>
@@ -6905,16 +6902,14 @@
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑太∼
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南フ南フ
-‹</t>
+南フ南フ</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -6956,8 +6951,7 @@
       <c r="T8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南∧
-南フ
-‹</t>
+南フ</t>
         </is>
       </c>
       <c r="U8" s="24"/>
@@ -7139,8 +7133,7 @@
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–ㄴ∼
-南ㅅ)
-‹</t>
+南ㅅ)</t>
         </is>
       </c>
       <c r="I11" s="24" t="inlineStr">
@@ -7178,8 +7171,7 @@
       <c r="Q11" s="24"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南)ㅅ
-‹</t>
+          <t xml:space="preserve">南)ㅅ</t>
         </is>
       </c>
       <c r="S11" s="24"/>
@@ -7272,8 +7264,7 @@
       <c r="T12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰∧
-㴌∧
-‹</t>
+㴌∧</t>
         </is>
       </c>
       <c r="U12" s="22"/>
@@ -7405,8 +7396,7 @@
       <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-湳∧
-‹</t>
+湳∧</t>
         </is>
       </c>
       <c r="U14" s="24"/>
@@ -7467,8 +7457,7 @@
       <c r="N17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳∧
-淋ʒ
-‹</t>
+淋ʒ</t>
         </is>
       </c>
       <c r="O17" s="22"/>
@@ -7559,15 +7548,13 @@
       <c r="J19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰∧Z
-‹</t>
+汰∧Z</t>
         </is>
       </c>
       <c r="K19" s="24"/>
       <c r="L19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="M19" s="24"/>
@@ -7576,16 +7563,14 @@
       <c r="P19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南フ
-南フ
-‹</t>
+南フ</t>
         </is>
       </c>
       <c r="Q19" s="24"/>
       <c r="R19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南フ
-南フ
-‹</t>
+南フ</t>
         </is>
       </c>
       <c r="S19" s="24"/>
@@ -7623,8 +7608,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹フ
-‹</t>
+          <t xml:space="preserve">浹フ</t>
         </is>
       </c>
       <c r="O20" s="22"/>
@@ -7718,23 +7702,20 @@
       <c r="L22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞ʒ
-湳フ
-‹</t>
+湳フ</t>
         </is>
       </c>
       <c r="M22" s="24"/>
       <c r="N22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">)
-‹</t>
+          <t xml:space="preserve">)</t>
         </is>
       </c>
       <c r="O22" s="24"/>
       <c r="P22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南∧
-南フ
-‹</t>
+南フ</t>
         </is>
       </c>
       <c r="Q22" s="24"/>
@@ -7866,8 +7847,7 @@
       <c r="K25" s="24"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㅅ
-‹</t>
+          <t xml:space="preserve">汰ㅅ</t>
         </is>
       </c>
       <c r="M25" s="24"/>
@@ -7875,8 +7855,7 @@
       <c r="O25" s="24"/>
       <c r="P25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">И
-‹</t>
+          <t xml:space="preserve">И</t>
         </is>
       </c>
       <c r="Q25" s="24"/>
@@ -7926,8 +7905,7 @@
       <c r="P26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰∧
-㴌∧
-‹</t>
+㴌∧</t>
         </is>
       </c>
       <c r="Q26" s="22"/>
@@ -7935,7 +7913,7 @@
       <c r="S26" s="22"/>
       <c r="T26" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">?∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="U26" s="29"/>

--- a/sheets/대금율보/검수/긴아리랑.xlsx
+++ b/sheets/대금율보/검수/긴아리랑.xlsx
@@ -6475,32 +6475,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="19.86" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="19.86" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="19.86" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="19.86" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="19.86" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="19.86" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="19.86" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="19.86" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="19.86" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="19.86" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="125.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="186.57" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="186.57" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="186.57" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="186.57" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="186.57" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -6883,7 +6883,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="186.57" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="186.57" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="186.57" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="186.57" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="186.57" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="186.57" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="186.57" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -7401,10 +7401,10 @@
       </c>
       <c r="U14" s="24"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="125.0" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="186.57" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="186.57" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -7535,7 +7535,7 @@
       <c r="T18" s="21"/>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="186.57" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="U19" s="24"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="186.57" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -7641,7 +7641,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="186.57" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -7682,7 +7682,7 @@
       <c r="T21" s="21"/>
       <c r="U21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="186.57" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="186.57" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -7787,7 +7787,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="186.57" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="U24" s="23"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="186.57" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="186.57" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="U26" s="29"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="186.57" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -7954,7 +7954,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="186.57" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -8008,7 +8008,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="32"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
